--- a/data/marketlogins.xlsx
+++ b/data/marketlogins.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IBS NL62\PycharmProjects\PythonProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E29D8E-414C-4117-8E21-653A9B8446F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78385157-0DDF-4154-8BFD-9186152182F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{B868D1A5-722E-4BB5-857C-FD1FB6EABAD3}"/>
   </bookViews>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -662,7 +662,7 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -673,7 +673,7 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
